--- a/content/table1.xlsx
+++ b/content/table1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c72363082c40911d/doc/WXiao/web app/CodeM/content/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1d8c3d380d53cb8/Desktop/沐恩中文学习/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_F25DC773A252ABDACC10484FB9DE559E5ADE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72C92503-1224-4C2E-A9F4-CA18F24B6A60}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="11_F25DC773A252ABDACC10484FB9DE559E5ADE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{682AC08D-7D16-4D58-A6DC-5BA940C6796E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="52">
   <si>
     <t>答案</t>
   </si>
@@ -46,130 +46,142 @@
     <t>index r</t>
   </si>
   <si>
-    <t>压机</t>
-  </si>
-  <si>
-    <t>一</t>
-  </si>
-  <si>
-    <t>西瓜</t>
-  </si>
-  <si>
-    <t>二</t>
-  </si>
-  <si>
-    <t>医生</t>
-  </si>
-  <si>
-    <t>老师</t>
-  </si>
-  <si>
-    <t>三</t>
-  </si>
-  <si>
-    <t>对不起</t>
-  </si>
-  <si>
-    <t>谢谢</t>
-  </si>
-  <si>
-    <t>四</t>
-  </si>
-  <si>
-    <t>香蕉</t>
-  </si>
-  <si>
-    <t>护士</t>
-  </si>
-  <si>
-    <t>五</t>
-  </si>
-  <si>
-    <t>六</t>
-  </si>
-  <si>
-    <t>你好</t>
-  </si>
-  <si>
-    <t>七</t>
-  </si>
-  <si>
-    <t>八</t>
-  </si>
-  <si>
-    <t>九</t>
-  </si>
-  <si>
-    <t>十</t>
-  </si>
-  <si>
-    <t>十一</t>
-  </si>
-  <si>
-    <t>十二</t>
-  </si>
-  <si>
-    <t>十三</t>
-  </si>
-  <si>
-    <t>十四</t>
-  </si>
-  <si>
-    <t>十五</t>
-  </si>
-  <si>
-    <t>十六</t>
-  </si>
-  <si>
-    <t>十七</t>
-  </si>
-  <si>
-    <t>十八</t>
-  </si>
-  <si>
-    <t>十九</t>
-  </si>
-  <si>
-    <t>二十</t>
-  </si>
-  <si>
     <t>Round1</t>
   </si>
   <si>
     <t>Round2</t>
   </si>
   <si>
-    <t>大风大雨</t>
-  </si>
-  <si>
-    <t>白云</t>
-  </si>
-  <si>
-    <t>红花</t>
-  </si>
-  <si>
-    <t>手上</t>
-  </si>
-  <si>
-    <t>白天鹅</t>
-  </si>
-  <si>
-    <t>毛毛虫</t>
-  </si>
-  <si>
-    <t>我对了</t>
-  </si>
-  <si>
-    <t>鸟毛</t>
-  </si>
-  <si>
-    <t>不去了</t>
-  </si>
-  <si>
-    <t>山水</t>
-  </si>
-  <si>
-    <t>王子</t>
+    <t>春天</t>
+  </si>
+  <si>
+    <t>寻找</t>
+  </si>
+  <si>
+    <t>姑娘</t>
+  </si>
+  <si>
+    <t>仔细</t>
+  </si>
+  <si>
+    <t>野花</t>
+  </si>
+  <si>
+    <t>柳枝</t>
+  </si>
+  <si>
+    <t>秋千</t>
+  </si>
+  <si>
+    <t>桃花</t>
+  </si>
+  <si>
+    <t>杏花</t>
+  </si>
+  <si>
+    <t>鲜花</t>
+  </si>
+  <si>
+    <t>歌咏</t>
+  </si>
+  <si>
+    <t>游泳</t>
+  </si>
+  <si>
+    <t>春花</t>
+  </si>
+  <si>
+    <t>柳支</t>
+  </si>
+  <si>
+    <t>迎枝</t>
+  </si>
+  <si>
+    <t>寻我</t>
+  </si>
+  <si>
+    <t>找寻</t>
+  </si>
+  <si>
+    <t>娘娘</t>
+  </si>
+  <si>
+    <t>姑姑</t>
+  </si>
+  <si>
+    <t>厨房</t>
+  </si>
+  <si>
+    <t>厕房</t>
+  </si>
+  <si>
+    <t>厢房</t>
+  </si>
+  <si>
+    <t>厕所</t>
+  </si>
+  <si>
+    <t>厦所</t>
+  </si>
+  <si>
+    <t>厘所</t>
+  </si>
+  <si>
+    <t>大厦</t>
+  </si>
+  <si>
+    <t>太厦</t>
+  </si>
+  <si>
+    <t>大夏</t>
+  </si>
+  <si>
+    <t>洞穴</t>
+  </si>
+  <si>
+    <t>同穴</t>
+  </si>
+  <si>
+    <t>洞窑</t>
+  </si>
+  <si>
+    <t>窑洞</t>
+  </si>
+  <si>
+    <t>窄洞</t>
+  </si>
+  <si>
+    <t>窑冻</t>
+  </si>
+  <si>
+    <t>窟窿</t>
+  </si>
+  <si>
+    <t>屈隆</t>
+  </si>
+  <si>
+    <t>窄窿</t>
+  </si>
+  <si>
+    <t>马棚</t>
+  </si>
+  <si>
+    <t>马朋</t>
+  </si>
+  <si>
+    <t>马篷</t>
+  </si>
+  <si>
+    <t>驮袋子</t>
+  </si>
+  <si>
+    <t>驮带子</t>
+  </si>
+  <si>
+    <t>驮袋了</t>
+  </si>
+  <si>
+    <t>驼袋子</t>
   </si>
 </sst>
 </file>
@@ -222,6 +234,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -487,10 +503,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -510,18 +526,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -530,18 +546,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -550,18 +566,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -570,18 +586,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -590,18 +606,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -610,18 +626,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -630,18 +646,18 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -650,18 +666,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -670,18 +686,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -690,18 +706,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -710,18 +726,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -730,184 +746,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="E13">
         <v>12</v>
       </c>
       <c r="F13">
         <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14">
-        <v>13</v>
-      </c>
-      <c r="F14">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15">
-        <v>14</v>
-      </c>
-      <c r="F15">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16">
-        <v>15</v>
-      </c>
-      <c r="F16">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17">
-        <v>16</v>
-      </c>
-      <c r="F17">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18">
-        <v>17</v>
-      </c>
-      <c r="F18">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>32</v>
-      </c>
-      <c r="B19" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" t="s">
-        <v>16</v>
-      </c>
-      <c r="D19" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19">
-        <v>18</v>
-      </c>
-      <c r="F19">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>33</v>
-      </c>
-      <c r="B20" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20">
-        <v>19</v>
-      </c>
-      <c r="F20">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>34</v>
-      </c>
-      <c r="B21" t="s">
-        <v>34</v>
-      </c>
-      <c r="C21" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" t="s">
-        <v>11</v>
-      </c>
-      <c r="E21">
-        <v>20</v>
-      </c>
-      <c r="F21">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -918,59 +774,62 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{848712EF-7B72-49FE-9D05-1DC01A55E119}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/content/table1.xlsx
+++ b/content/table1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1d8c3d380d53cb8/Desktop/沐恩中文学习/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="11_F25DC773A252ABDACC10484FB9DE559E5ADE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{682AC08D-7D16-4D58-A6DC-5BA940C6796E}"/>
+  <xr:revisionPtr revIDLastSave="76" documentId="11_F25DC773A252ABDACC10484FB9DE559E5ADE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A246E73A-3BA8-485E-8454-C620FBE1C0E6}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="51">
   <si>
     <t>答案</t>
   </si>
@@ -179,9 +179,6 @@
   </si>
   <si>
     <t>驮袋了</t>
-  </si>
-  <si>
-    <t>驼袋子</t>
   </si>
 </sst>
 </file>
@@ -737,7 +734,7 @@
         <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -757,7 +754,7 @@
         <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E13">
         <v>12</v>
